--- a/output/pdf_financials_xlsx/CQR.xlsx
+++ b/output/pdf_financials_xlsx/CQR.xlsx
@@ -1173,19 +1173,19 @@
         <v>-0.171</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.436619</v>
@@ -1425,19 +1425,19 @@
         <v>-0.171</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0.436619</v>
@@ -1572,19 +1572,19 @@
         <v>-0.171</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0.436619</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>134.192367</v>
+        <v>-134.192367</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1802,19 +1802,19 @@
         <v>-0.171</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0.436619</v>
@@ -1900,19 +1900,19 @@
         <v>-0.171</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.436619</v>
@@ -2022,19 +2022,19 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>0</v>
@@ -5099,46 +5099,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.06469</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.931965</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.010375</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.028453</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.957402</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.957402</v>
       </c>
     </row>
     <row r="93">
@@ -8296,7 +8296,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8844,7 +8848,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -9350,7 +9358,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11772,7 +11784,11 @@
           <t>Share-based payment reserve 10 67,000</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -12914,7 +12930,11 @@
           <t>Share-based payment reserve 11 151</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -13600,7 +13620,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -14900,7 +14924,11 @@
           <t>Share-based payment reserve 11 (d) 262</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.349</v>
       </c>
@@ -26643,10 +26671,10 @@
         </is>
       </c>
       <c r="N228" s="5" t="n">
-        <v>4.025771</v>
+        <v>-4.025771</v>
       </c>
       <c r="O228" s="5" t="n">
-        <v>0.842191</v>
+        <v>-0.842191</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -27050,13 +27078,13 @@
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>0.170195</v>
+        <v>-0.170195</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>0.44008</v>
+        <v>-0.44008</v>
       </c>
       <c r="M233" s="5" t="n">
-        <v>0.214436</v>
+        <v>-0.214436</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CQR.xlsx
+++ b/output/pdf_financials_xlsx/CQR.xlsx
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -986,19 +986,19 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007142</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015297</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.043424</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039156</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014139</v>
       </c>
     </row>
     <row r="13">
@@ -1787,7 +1787,7 @@
         <v>2.048</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.681</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.378</v>
@@ -1811,19 +1811,19 @@
         <v>-0.214436</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.025771</v>
+        <v>-4.018629</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.842191</v>
+        <v>-0.826894</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.436619</v>
+        <v>0.480043</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.828712</v>
+        <v>-0.789556</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.323621</v>
+        <v>-0.309482</v>
       </c>
     </row>
     <row r="28">
@@ -1885,7 +1885,7 @@
         <v>2.048</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.679</v>
+        <v>-0.676</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.378</v>
@@ -1909,19 +1909,19 @@
         <v>-0.214436</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.025771</v>
+        <v>-4.018629</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.842191</v>
+        <v>-0.826894</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.436619</v>
+        <v>0.480043</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.828712</v>
+        <v>-0.789556</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.323621</v>
+        <v>-0.309482</v>
       </c>
     </row>
     <row r="30">
@@ -2139,10 +2139,10 @@
         <v>0.572</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.008999999999999999</v>
@@ -2151,13 +2151,13 @@
         <v>0.004</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.215635</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011292</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.252034</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.949588</v>
@@ -2237,10 +2237,10 @@
         <v>3.58</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.056</v>
+        <v>1.058</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.089</v>
@@ -2249,13 +2249,13 @@
         <v>0.355</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.001065</v>
+        <v>0.2167</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011292</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.252034</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.949588</v>
@@ -2825,10 +2825,10 @@
         <v>1.764</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -2837,13 +2837,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.219358</v>
+        <v>0.003723</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.015496</v>
+        <v>0.004204</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.252034</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
